--- a/tests/fixtures/02-Fails-03/studies/TalinumSamples-STRI/isa.study.xlsx
+++ b/tests/fixtures/02-Fails-03/studies/TalinumSamples-STRI/isa.study.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="193">
   <si>
     <t>Input [Source Name]</t>
   </si>
@@ -165,9 +165,6 @@
   </si>
   <si>
     <t>http://purl.org/nfdi4plants/ontology/dpbo/DPBO_1000164</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Talinum fruticosum</t>
@@ -633,12 +630,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -659,8 +653,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AT7" displayName="annotationTable0" name="annotationTable0" id="1" totalsRowShown="0">
-  <autoFilter ref="A1:AT7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AT8" displayName="annotationTable0" name="annotationTable0" id="1" totalsRowShown="0">
+  <autoFilter ref="A1:AT8">
     <filterColumn hiddenButton="1" colId="0"/>
     <filterColumn hiddenButton="1" colId="1"/>
     <filterColumn hiddenButton="1" colId="2"/>
@@ -1141,16 +1135,16 @@
   <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1159,10 +1153,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
       <c r="A2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1170,10 +1164,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
       <c r="A3" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1181,10 +1175,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
       <c r="A4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -1192,7 +1186,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
       <c r="A5" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1201,7 +1195,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
       <c r="A6" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1210,10 +1204,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
       <c r="A7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1221,7 +1215,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
       <c r="A8" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1230,10 +1224,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
       <c r="A9" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -1241,10 +1235,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
       <c r="A10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -1252,10 +1246,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
       <c r="A11" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -1263,7 +1257,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
       <c r="A12" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1272,7 +1266,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
       <c r="A13" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1281,7 +1275,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
       <c r="A14" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1290,7 +1284,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
       <c r="A15" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1299,7 +1293,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
       <c r="A16" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1308,7 +1302,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
       <c r="A17" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1317,7 +1311,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25">
       <c r="A18" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1326,7 +1320,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25">
       <c r="A19" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1335,7 +1329,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
       <c r="A20" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1344,7 +1338,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
       <c r="A21" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>33</v>
@@ -1361,50 +1355,50 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25">
       <c r="A22" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25">
       <c r="A23" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25">
       <c r="A24" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="17.25">
       <c r="A25" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1413,22 +1407,22 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
       <c r="A26" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="E26" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25">
       <c r="A27" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1437,7 +1431,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
       <c r="A28" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1446,23 +1440,23 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25">
       <c r="A29" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25">
       <c r="A30" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -1470,10 +1464,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
       <c r="A31" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -1481,10 +1475,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
       <c r="A32" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -1492,10 +1486,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25">
       <c r="A33" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -1503,10 +1497,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25">
       <c r="A34" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -1514,10 +1508,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
       <c r="A35" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -1525,22 +1519,22 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
       <c r="A36" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="E36" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
       <c r="A37" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1549,10 +1543,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
       <c r="A38" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -1560,7 +1554,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
       <c r="A39" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>47</v>
@@ -1571,7 +1565,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>49</v>
@@ -1582,7 +1576,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
       <c r="A41" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>48</v>
@@ -1593,7 +1587,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
       <c r="A42" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -1602,7 +1596,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
       <c r="A43" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -1611,7 +1605,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -1620,10 +1614,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -1631,10 +1625,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
       <c r="A46" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -1642,10 +1636,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -1653,7 +1647,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -1662,7 +1656,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -1671,7 +1665,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1680,7 +1674,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -1689,7 +1683,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
       <c r="A52" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -1698,33 +1692,33 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
       <c r="A53" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
       <c r="A54" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
       <c r="A55" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -1733,10 +1727,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
       <c r="A56" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -1744,10 +1738,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
       <c r="A57" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -1755,7 +1749,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
       <c r="A58" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -1764,75 +1758,75 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
       <c r="A59" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
       <c r="A60" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
       <c r="A61" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
       <c r="A62" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
       <c r="A63" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="C63" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
       <c r="A64" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -1848,55 +1842,55 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AT7"/>
+  <dimension ref="A1:AT8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="3" width="26.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="3" width="30.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="33" max="33" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="34" max="34" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="35" max="35" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="36" max="36" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="37" max="37" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="38" max="38" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="39" max="39" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="40" max="40" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="41" max="41" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="42" max="42" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="43" max="43" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="44" max="44" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="45" max="45" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="46" max="46" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="26.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="2" width="30.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="30" max="30" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="31" max="31" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="32" max="32" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="33" max="33" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="34" max="34" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="35" max="35" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="36" max="36" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="37" max="37" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="38" max="38" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="39" max="39" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="40" max="40" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="41" max="41" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="42" max="42" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="43" max="43" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="44" max="44" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="45" max="45" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="46" max="46" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
@@ -2052,124 +2046,112 @@
       <c r="D2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q2" s="1"/>
       <c r="R2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="X2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AB2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AE2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="AI2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ2" s="1"/>
       <c r="AK2" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AM2" s="1"/>
       <c r="AN2" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AP2" s="1"/>
       <c r="AQ2" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AS2" s="1"/>
       <c r="AT2" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
       <c r="A3" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>47</v>
@@ -2180,124 +2162,112 @@
       <c r="D3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q3" s="1"/>
       <c r="R3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="X3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AB3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AD3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AD3" s="1" t="s">
+      <c r="AE3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AE3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG3" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH3" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="AI3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AM3" s="1"/>
       <c r="AN3" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AP3" s="1"/>
       <c r="AQ3" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AR3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AS3" s="1"/>
       <c r="AT3" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
       <c r="A4" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>47</v>
@@ -2308,124 +2278,112 @@
       <c r="D4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="X4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AB4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AB4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC4" s="1" t="s">
+      <c r="AD4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AD4" s="1" t="s">
+      <c r="AE4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH4" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AE4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH4" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="AI4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AL4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AM4" s="1"/>
       <c r="AN4" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AO4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AR4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AS4" s="1"/>
       <c r="AT4" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
       <c r="A5" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>47</v>
@@ -2436,124 +2394,112 @@
       <c r="D5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="T5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="U5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="U5" s="1" t="s">
+      <c r="V5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="V5" s="1" t="s">
+      <c r="W5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="W5" s="1" t="s">
+      <c r="X5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y5" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="X5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y5" s="1" t="s">
+      <c r="Z5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Z5" s="1" t="s">
+      <c r="AA5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AA5" s="1" t="s">
+      <c r="AB5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC5" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AB5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC5" s="1" t="s">
+      <c r="AD5" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AD5" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="AE5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG5" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AF5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG5" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="AH5" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AL5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AR5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AS5" s="1"/>
       <c r="AT5" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
       <c r="A6" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>47</v>
@@ -2564,247 +2510,271 @@
       <c r="D6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q6" s="1"/>
       <c r="R6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="T6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="T6" s="1" t="s">
+      <c r="U6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="U6" s="1" t="s">
+      <c r="V6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="V6" s="1" t="s">
+      <c r="W6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="W6" s="1" t="s">
+      <c r="X6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y6" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="X6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y6" s="1" t="s">
+      <c r="Z6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Z6" s="1" t="s">
+      <c r="AA6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AA6" s="1" t="s">
+      <c r="AB6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AB6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC6" s="1" t="s">
+      <c r="AD6" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AD6" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="AE6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AF6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG6" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="AH6" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AL6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AM6" s="1"/>
       <c r="AN6" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AR6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AS6" s="1"/>
       <c r="AT6" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
+      <c r="AI7" s="1"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="1"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="1"/>
+      <c r="AO7" s="1"/>
+      <c r="AP7" s="1"/>
+      <c r="AQ7" s="1"/>
+      <c r="AR7" s="1"/>
+      <c r="AS7" s="1"/>
+      <c r="AT7" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
+      <c r="A8" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
-      <c r="A7" s="1" t="s">
+      <c r="B8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AL8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AM8" s="1"/>
+      <c r="AN8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AO8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP8" s="1"/>
+      <c r="AQ8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AR8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AS8" s="1"/>
+      <c r="AT8" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AE7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH7" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AJ7" s="1"/>
-      <c r="AK7" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AL7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AM7" s="1"/>
-      <c r="AN7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AO7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AP7" s="1"/>
-      <c r="AQ7" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AR7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AS7" s="1"/>
-      <c r="AT7" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
